--- a/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152324.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152324.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1A40232-20B5-4F6C-AB44-20B82FB35818}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F0119A0-5384-49FD-97C8-5C8A83DC6D89}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A4A9D50-EDEA-46CC-8531-B2F5E3D72921}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B033EB2-359F-452D-BDBE-902978B6D107}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA8CE608-C109-4D74-94B0-C812FAF45859}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64C4CC24-9F76-4DC1-9976-253E259EB8EC}"/>
 </file>
--- a/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152324.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152324.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F0119A0-5384-49FD-97C8-5C8A83DC6D89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1A40232-20B5-4F6C-AB44-20B82FB35818}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B033EB2-359F-452D-BDBE-902978B6D107}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A4A9D50-EDEA-46CC-8531-B2F5E3D72921}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64C4CC24-9F76-4DC1-9976-253E259EB8EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA8CE608-C109-4D74-94B0-C812FAF45859}"/>
 </file>